--- a/Solutions/Metapelite.xlsx
+++ b/Solutions/Metapelite.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dropbox\Thermolab\v_25_05_12\Solutions\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hans\Documents\GitHub\Thermolab\Solutions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21CBB769-D65B-4000-AB1C-C0D5D0592ABE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD6A350B-900D-469B-82E6-679D564323BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="12" xr2:uid="{D3EBF20D-CCE5-4C22-BBD8-B9FEED2226C6}"/>
+    <workbookView xWindow="18620" yWindow="3340" windowWidth="17100" windowHeight="16660" activeTab="2" xr2:uid="{D3EBF20D-CCE5-4C22-BBD8-B9FEED2226C6}"/>
   </bookViews>
   <sheets>
     <sheet name="Fluid" sheetId="28" r:id="rId1"/>
@@ -51,9 +51,6 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
@@ -676,9 +673,6 @@
     <t>mnct</t>
   </si>
   <si>
-    <t>S</t>
-  </si>
-  <si>
     <t>faq</t>
   </si>
   <si>
@@ -719,6 +713,9 @@
   </si>
   <si>
     <t>H2O,tc-ds62</t>
+  </si>
+  <si>
+    <t>pol</t>
   </si>
 </sst>
 </file>
@@ -789,9 +786,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -829,7 +826,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -935,7 +932,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1077,7 +1074,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1086,12 +1083,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9FECEDE1-30DF-4A64-98D4-F52E658212ED}">
   <dimension ref="A1:I18"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1099,7 +1096,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -1110,31 +1107,31 @@
         <v>46</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>4</v>
       </c>
       <c r="B4" t="s">
+        <v>215</v>
+      </c>
+      <c r="C4" t="s">
         <v>216</v>
       </c>
-      <c r="C4" t="s">
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
         <v>217</v>
       </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+      <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
         <v>218</v>
-      </c>
-      <c r="B6">
-        <v>1</v>
-      </c>
-      <c r="C6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>219</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -1146,7 +1143,7 @@
       <c r="H7" s="1"/>
       <c r="I7" s="1"/>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>10</v>
       </c>
@@ -1160,12 +1157,12 @@
       <c r="H9" s="1"/>
       <c r="I9" s="1"/>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
       <c r="G10" s="1"/>
       <c r="H10" s="1"/>
       <c r="I10" s="1"/>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>11</v>
       </c>
@@ -1176,7 +1173,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>12</v>
       </c>
@@ -1187,7 +1184,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>13</v>
       </c>
@@ -1199,7 +1196,7 @@
         <v>1.1111111111111112E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>14</v>
       </c>
@@ -1210,11 +1207,11 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="7:8" x14ac:dyDescent="0.25">
+    <row r="17" spans="7:8" x14ac:dyDescent="0.35">
       <c r="G17" s="1"/>
       <c r="H17" s="1"/>
     </row>
-    <row r="18" spans="7:8" x14ac:dyDescent="0.25">
+    <row r="18" spans="7:8" x14ac:dyDescent="0.35">
       <c r="G18" s="1"/>
       <c r="H18" s="1"/>
     </row>
@@ -1226,12 +1223,12 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A6C80D66-2E8F-4748-B373-E923324DC424}">
   <dimension ref="A1:K47"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1239,7 +1236,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -1274,7 +1271,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -1309,7 +1306,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>81</v>
       </c>
@@ -1344,7 +1341,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>82</v>
       </c>
@@ -1379,7 +1376,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>83</v>
       </c>
@@ -1414,7 +1411,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>84</v>
       </c>
@@ -1449,9 +1446,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -1484,7 +1481,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>85</v>
       </c>
@@ -1519,7 +1516,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>10</v>
       </c>
@@ -1554,7 +1551,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>11</v>
       </c>
@@ -1589,7 +1586,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>12</v>
       </c>
@@ -1624,7 +1621,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>13</v>
       </c>
@@ -1669,7 +1666,7 @@
         <v>0.16666666666666666</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>14</v>
       </c>
@@ -1704,7 +1701,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>15</v>
       </c>
@@ -1727,7 +1724,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>76</v>
       </c>
@@ -1750,7 +1747,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>77</v>
       </c>
@@ -1773,7 +1770,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>78</v>
       </c>
@@ -1796,7 +1793,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>79</v>
       </c>
@@ -1819,7 +1816,7 @@
         <v>30000</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>96</v>
       </c>
@@ -1842,7 +1839,7 @@
         <v>35000</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>80</v>
       </c>
@@ -1865,7 +1862,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>20</v>
       </c>
@@ -1888,7 +1885,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>76</v>
       </c>
@@ -1912,7 +1909,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>77</v>
       </c>
@@ -1935,7 +1932,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>78</v>
       </c>
@@ -1958,7 +1955,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>79</v>
       </c>
@@ -1982,7 +1979,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>96</v>
       </c>
@@ -2005,7 +2002,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>80</v>
       </c>
@@ -2028,7 +2025,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>21</v>
       </c>
@@ -2051,7 +2048,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>76</v>
       </c>
@@ -2074,7 +2071,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>77</v>
       </c>
@@ -2097,7 +2094,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>78</v>
       </c>
@@ -2120,7 +2117,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>79</v>
       </c>
@@ -2143,7 +2140,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>96</v>
       </c>
@@ -2166,7 +2163,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>80</v>
       </c>
@@ -2189,7 +2186,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>22</v>
       </c>
@@ -2212,7 +2209,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>23</v>
       </c>
@@ -2235,7 +2232,7 @@
         <v>0.63</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>24</v>
       </c>
@@ -2258,7 +2255,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>25</v>
       </c>
@@ -2289,12 +2286,12 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{283EBC83-024D-4274-A3E3-5FB71B51C0FA}">
   <dimension ref="A1:K47"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2302,7 +2299,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -2337,7 +2334,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -2372,7 +2369,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>81</v>
       </c>
@@ -2407,7 +2404,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>82</v>
       </c>
@@ -2442,7 +2439,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>83</v>
       </c>
@@ -2477,7 +2474,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>84</v>
       </c>
@@ -2512,9 +2509,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -2547,7 +2544,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>85</v>
       </c>
@@ -2582,7 +2579,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>10</v>
       </c>
@@ -2617,7 +2614,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>11</v>
       </c>
@@ -2652,7 +2649,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>12</v>
       </c>
@@ -2687,7 +2684,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>13</v>
       </c>
@@ -2732,7 +2729,7 @@
         <v>0.16666666666666666</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>14</v>
       </c>
@@ -2767,7 +2764,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>15</v>
       </c>
@@ -2790,7 +2787,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>76</v>
       </c>
@@ -2813,7 +2810,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>77</v>
       </c>
@@ -2836,7 +2833,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>78</v>
       </c>
@@ -2859,7 +2856,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>79</v>
       </c>
@@ -2882,7 +2879,7 @@
         <v>30000</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>96</v>
       </c>
@@ -2905,7 +2902,7 @@
         <v>35000</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>80</v>
       </c>
@@ -2928,7 +2925,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>20</v>
       </c>
@@ -2951,7 +2948,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>76</v>
       </c>
@@ -2975,7 +2972,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>77</v>
       </c>
@@ -2998,7 +2995,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>78</v>
       </c>
@@ -3021,7 +3018,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>79</v>
       </c>
@@ -3045,7 +3042,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>96</v>
       </c>
@@ -3068,7 +3065,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>80</v>
       </c>
@@ -3091,7 +3088,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>21</v>
       </c>
@@ -3114,7 +3111,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>76</v>
       </c>
@@ -3137,7 +3134,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>77</v>
       </c>
@@ -3160,7 +3157,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>78</v>
       </c>
@@ -3183,7 +3180,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>79</v>
       </c>
@@ -3206,7 +3203,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>96</v>
       </c>
@@ -3229,7 +3226,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>80</v>
       </c>
@@ -3252,7 +3249,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>22</v>
       </c>
@@ -3275,7 +3272,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>23</v>
       </c>
@@ -3298,7 +3295,7 @@
         <v>0.63</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>24</v>
       </c>
@@ -3321,7 +3318,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>25</v>
       </c>
@@ -3352,12 +3349,12 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{43F8E32D-4936-4408-8429-41BE4C5BC6D8}">
   <dimension ref="A1:N28"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3365,7 +3362,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -3409,7 +3406,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -3453,7 +3450,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>108</v>
       </c>
@@ -3497,7 +3494,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>109</v>
       </c>
@@ -3541,7 +3538,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>110</v>
       </c>
@@ -3585,7 +3582,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>111</v>
       </c>
@@ -3629,7 +3626,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>112</v>
       </c>
@@ -3673,7 +3670,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>113</v>
       </c>
@@ -3717,9 +3714,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -3761,7 +3758,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>10</v>
       </c>
@@ -3805,7 +3802,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>11</v>
       </c>
@@ -3849,7 +3846,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>12</v>
       </c>
@@ -3893,7 +3890,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>13</v>
       </c>
@@ -3950,7 +3947,7 @@
         <v>0.16666666666666666</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>14</v>
       </c>
@@ -3994,7 +3991,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>15</v>
       </c>
@@ -4017,10 +4014,10 @@
         <v>107</v>
       </c>
       <c r="H21" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>102</v>
       </c>
@@ -4046,7 +4043,7 @@
         <v>9000</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>103</v>
       </c>
@@ -4072,7 +4069,7 @@
         <v>6300</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>104</v>
       </c>
@@ -4098,7 +4095,7 @@
         <v>8100</v>
       </c>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>105</v>
       </c>
@@ -4124,7 +4121,7 @@
         <v>13000</v>
       </c>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>106</v>
       </c>
@@ -4150,7 +4147,7 @@
         <v>30000</v>
       </c>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>107</v>
       </c>
@@ -4176,9 +4173,9 @@
         <v>11600</v>
       </c>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B28">
         <v>9000</v>
@@ -4210,12 +4207,12 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{301C9287-71A8-4CE9-AB02-D4E51B5D2794}">
   <dimension ref="A1:L51"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -4223,7 +4220,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -4261,7 +4258,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -4299,7 +4296,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>120</v>
       </c>
@@ -4337,7 +4334,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>121</v>
       </c>
@@ -4375,7 +4372,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>122</v>
       </c>
@@ -4413,7 +4410,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>124</v>
       </c>
@@ -4451,7 +4448,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>125</v>
       </c>
@@ -4489,7 +4486,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>126</v>
       </c>
@@ -4527,7 +4524,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>123</v>
       </c>
@@ -4565,7 +4562,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>10</v>
       </c>
@@ -4603,7 +4600,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>11</v>
       </c>
@@ -4641,7 +4638,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>12</v>
       </c>
@@ -4679,7 +4676,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>13</v>
       </c>
@@ -4688,7 +4685,7 @@
         <v>0.33333333333333331</v>
       </c>
       <c r="C18">
-        <f t="shared" ref="C18:Q18" si="0">1/3</f>
+        <f t="shared" ref="C18:L18" si="0">1/3</f>
         <v>0.33333333333333331</v>
       </c>
       <c r="D18">
@@ -4728,7 +4725,7 @@
         <v>0.33333333333333331</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>14</v>
       </c>
@@ -4766,7 +4763,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>15</v>
       </c>
@@ -4792,7 +4789,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>115</v>
       </c>
@@ -4818,7 +4815,7 @@
         <v>32200</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>116</v>
       </c>
@@ -4844,7 +4841,7 @@
         <v>25540</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>117</v>
       </c>
@@ -4870,7 +4867,7 @@
         <v>22540</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>119</v>
       </c>
@@ -4896,7 +4893,7 @@
         <v>75400</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>127</v>
       </c>
@@ -4922,7 +4919,7 @@
         <v>73400</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>128</v>
       </c>
@@ -4948,7 +4945,7 @@
         <v>24540</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>118</v>
       </c>
@@ -4974,7 +4971,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>20</v>
       </c>
@@ -5000,7 +4997,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>115</v>
       </c>
@@ -5026,7 +5023,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>116</v>
       </c>
@@ -5052,7 +5049,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>117</v>
       </c>
@@ -5078,7 +5075,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>119</v>
       </c>
@@ -5104,7 +5101,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>127</v>
       </c>
@@ -5130,7 +5127,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>128</v>
       </c>
@@ -5156,7 +5153,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>118</v>
       </c>
@@ -5182,7 +5179,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>21</v>
       </c>
@@ -5208,7 +5205,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>115</v>
       </c>
@@ -5234,7 +5231,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>116</v>
       </c>
@@ -5260,7 +5257,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>117</v>
       </c>
@@ -5286,7 +5283,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>119</v>
       </c>
@@ -5312,7 +5309,7 @@
         <v>-940</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>127</v>
       </c>
@@ -5338,7 +5335,7 @@
         <v>-940</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>128</v>
       </c>
@@ -5364,7 +5361,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>118</v>
       </c>
@@ -5390,7 +5387,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>22</v>
       </c>
@@ -5416,7 +5413,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>23</v>
       </c>
@@ -5442,7 +5439,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>24</v>
       </c>
@@ -5468,7 +5465,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>25</v>
       </c>
@@ -5502,12 +5499,12 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3FC16AED-EAC3-438A-857D-79B21E8AB45C}">
   <dimension ref="A1:L51"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -5515,7 +5512,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -5553,7 +5550,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -5591,7 +5588,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>120</v>
       </c>
@@ -5629,7 +5626,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>121</v>
       </c>
@@ -5667,7 +5664,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>122</v>
       </c>
@@ -5705,7 +5702,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>124</v>
       </c>
@@ -5743,7 +5740,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>125</v>
       </c>
@@ -5781,7 +5778,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>126</v>
       </c>
@@ -5819,7 +5816,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>123</v>
       </c>
@@ -5857,7 +5854,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>10</v>
       </c>
@@ -5895,7 +5892,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>11</v>
       </c>
@@ -5933,7 +5930,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>12</v>
       </c>
@@ -5971,7 +5968,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>13</v>
       </c>
@@ -6020,7 +6017,7 @@
         <v>0.33333333333333331</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>14</v>
       </c>
@@ -6058,7 +6055,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>15</v>
       </c>
@@ -6084,7 +6081,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>115</v>
       </c>
@@ -6110,7 +6107,7 @@
         <v>32200</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>116</v>
       </c>
@@ -6136,7 +6133,7 @@
         <v>25540</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>117</v>
       </c>
@@ -6162,7 +6159,7 @@
         <v>22540</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>119</v>
       </c>
@@ -6188,7 +6185,7 @@
         <v>75400</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>127</v>
       </c>
@@ -6214,7 +6211,7 @@
         <v>73400</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>128</v>
       </c>
@@ -6240,7 +6237,7 @@
         <v>24540</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>118</v>
       </c>
@@ -6266,7 +6263,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>20</v>
       </c>
@@ -6292,7 +6289,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>115</v>
       </c>
@@ -6318,7 +6315,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>116</v>
       </c>
@@ -6344,7 +6341,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>117</v>
       </c>
@@ -6370,7 +6367,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>119</v>
       </c>
@@ -6396,7 +6393,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>127</v>
       </c>
@@ -6422,7 +6419,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>128</v>
       </c>
@@ -6448,7 +6445,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>118</v>
       </c>
@@ -6474,7 +6471,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>21</v>
       </c>
@@ -6500,7 +6497,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>115</v>
       </c>
@@ -6526,7 +6523,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>116</v>
       </c>
@@ -6552,7 +6549,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>117</v>
       </c>
@@ -6578,7 +6575,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>119</v>
       </c>
@@ -6604,7 +6601,7 @@
         <v>-940</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>127</v>
       </c>
@@ -6630,7 +6627,7 @@
         <v>-940</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>128</v>
       </c>
@@ -6656,7 +6653,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>118</v>
       </c>
@@ -6682,7 +6679,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>22</v>
       </c>
@@ -6708,7 +6705,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>23</v>
       </c>
@@ -6734,7 +6731,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>24</v>
       </c>
@@ -6760,7 +6757,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>25</v>
       </c>
@@ -6795,12 +6792,12 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B372060-0513-48CB-BA54-2F23733466FB}">
   <dimension ref="A1:L31"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -6808,7 +6805,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -6837,7 +6834,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -6866,7 +6863,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>130</v>
       </c>
@@ -6895,7 +6892,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>131</v>
       </c>
@@ -6924,7 +6921,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>132</v>
       </c>
@@ -6953,7 +6950,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>133</v>
       </c>
@@ -6982,7 +6979,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>134</v>
       </c>
@@ -7011,7 +7008,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>10</v>
       </c>
@@ -7042,7 +7039,7 @@
       <c r="K12" s="1"/>
       <c r="L12" s="1"/>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>11</v>
       </c>
@@ -7071,7 +7068,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>12</v>
       </c>
@@ -7100,7 +7097,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>13</v>
       </c>
@@ -7137,7 +7134,7 @@
         <v>0.33333333333333331</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>14</v>
       </c>
@@ -7166,7 +7163,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>15</v>
       </c>
@@ -7186,7 +7183,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>135</v>
       </c>
@@ -7206,7 +7203,7 @@
         <v>8000</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>136</v>
       </c>
@@ -7226,7 +7223,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>137</v>
       </c>
@@ -7246,7 +7243,7 @@
         <v>17600</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>138</v>
       </c>
@@ -7266,7 +7263,7 @@
         <v>20000</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>139</v>
       </c>
@@ -7286,7 +7283,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>21</v>
       </c>
@@ -7306,7 +7303,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>135</v>
       </c>
@@ -7326,7 +7323,7 @@
         <v>-20</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>136</v>
       </c>
@@ -7346,7 +7343,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>137</v>
       </c>
@@ -7366,7 +7363,7 @@
         <v>-20</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>138</v>
       </c>
@@ -7386,7 +7383,7 @@
         <v>-20</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>139</v>
       </c>
@@ -7414,12 +7411,12 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57B32511-7A8C-4FC6-B261-ACCBDD36F7C7}">
   <dimension ref="A1:F22"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -7427,7 +7424,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -7447,7 +7444,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -7467,7 +7464,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>140</v>
       </c>
@@ -7487,7 +7484,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>141</v>
       </c>
@@ -7507,7 +7504,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>142</v>
       </c>
@@ -7527,7 +7524,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>197</v>
       </c>
@@ -7547,7 +7544,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>10</v>
       </c>
@@ -7567,7 +7564,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>11</v>
       </c>
@@ -7587,7 +7584,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>12</v>
       </c>
@@ -7607,7 +7604,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>13</v>
       </c>
@@ -7632,7 +7629,7 @@
         <v>0.16666666666666666</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>14</v>
       </c>
@@ -7652,7 +7649,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>15</v>
       </c>
@@ -7669,7 +7666,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>143</v>
       </c>
@@ -7686,7 +7683,7 @@
         <v>6000</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>144</v>
       </c>
@@ -7703,7 +7700,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>145</v>
       </c>
@@ -7720,7 +7717,7 @@
         <v>6000</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>198</v>
       </c>
@@ -7745,12 +7742,12 @@
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55948CD3-FAED-436F-8E63-0CD71E3896E0}">
   <dimension ref="A1:H24"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -7758,7 +7755,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -7784,7 +7781,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -7810,7 +7807,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>199</v>
       </c>
@@ -7836,7 +7833,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>149</v>
       </c>
@@ -7862,7 +7859,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>200</v>
       </c>
@@ -7888,7 +7885,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>150</v>
       </c>
@@ -7914,7 +7911,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>151</v>
       </c>
@@ -7942,7 +7939,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>10</v>
       </c>
@@ -7968,7 +7965,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>11</v>
       </c>
@@ -7994,7 +7991,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>12</v>
       </c>
@@ -8020,7 +8017,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>13</v>
       </c>
@@ -8053,7 +8050,7 @@
         <v>0.16666666666666666</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>14</v>
       </c>
@@ -8079,7 +8076,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>15</v>
       </c>
@@ -8099,7 +8096,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>202</v>
       </c>
@@ -8119,7 +8116,7 @@
         <v>20000</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>146</v>
       </c>
@@ -8139,7 +8136,7 @@
         <v>36000</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>201</v>
       </c>
@@ -8159,7 +8156,7 @@
         <v>32000</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>147</v>
       </c>
@@ -8179,7 +8176,7 @@
         <v>30000</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>148</v>
       </c>
@@ -8207,12 +8204,12 @@
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2ECBBB18-929D-4CB3-98BC-5E4CA97F1D1A}">
   <dimension ref="A1:N30"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -8220,7 +8217,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -8264,7 +8261,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -8308,7 +8305,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>161</v>
       </c>
@@ -8352,7 +8349,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>162</v>
       </c>
@@ -8396,7 +8393,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>163</v>
       </c>
@@ -8440,7 +8437,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>164</v>
       </c>
@@ -8484,7 +8481,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>165</v>
       </c>
@@ -8528,7 +8525,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>166</v>
       </c>
@@ -8572,7 +8569,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>167</v>
       </c>
@@ -8616,7 +8613,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>192</v>
       </c>
@@ -8660,7 +8657,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>10</v>
       </c>
@@ -8704,7 +8701,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>11</v>
       </c>
@@ -8748,7 +8745,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>12</v>
       </c>
@@ -8792,7 +8789,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>13</v>
       </c>
@@ -8849,7 +8846,7 @@
         <v>0.16666666666666666</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>14</v>
       </c>
@@ -8893,7 +8890,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>15</v>
       </c>
@@ -8922,7 +8919,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>154</v>
       </c>
@@ -8951,7 +8948,7 @@
         <v>6000</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>155</v>
       </c>
@@ -8980,7 +8977,7 @@
         <v>23000</v>
       </c>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>156</v>
       </c>
@@ -9009,7 +9006,7 @@
         <v>17000</v>
       </c>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>157</v>
       </c>
@@ -9038,7 +9035,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>158</v>
       </c>
@@ -9067,7 +9064,7 @@
         <v>19000</v>
       </c>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>159</v>
       </c>
@@ -9096,7 +9093,7 @@
         <v>22000</v>
       </c>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>160</v>
       </c>
@@ -9125,7 +9122,7 @@
         <v>8000</v>
       </c>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>193</v>
       </c>
@@ -9163,12 +9160,12 @@
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5153D3A6-C9BF-41F2-99DD-B46043608EB3}">
   <dimension ref="A1:F22"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -9176,7 +9173,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -9196,7 +9193,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -9216,7 +9213,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>194</v>
       </c>
@@ -9237,7 +9234,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>195</v>
       </c>
@@ -9258,7 +9255,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>203</v>
       </c>
@@ -9279,7 +9276,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>196</v>
       </c>
@@ -9300,7 +9297,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>10</v>
       </c>
@@ -9320,7 +9317,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>11</v>
       </c>
@@ -9340,7 +9337,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>12</v>
       </c>
@@ -9360,7 +9357,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>13</v>
       </c>
@@ -9385,7 +9382,7 @@
         <v>0.16666666666666666</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>14</v>
       </c>
@@ -9405,7 +9402,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>15</v>
       </c>
@@ -9422,7 +9419,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>170</v>
       </c>
@@ -9439,7 +9436,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>171</v>
       </c>
@@ -9456,7 +9453,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>204</v>
       </c>
@@ -9473,7 +9470,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>172</v>
       </c>
@@ -9498,15 +9495,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F4A4202-8327-4E7A-9AFF-5A01BE875B91}">
   <dimension ref="A1:G29"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="16.28515625" customWidth="1"/>
-    <col min="2" max="2" width="9.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.26953125" customWidth="1"/>
+    <col min="2" max="2" width="9.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.54296875" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="9.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -9514,7 +9511,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -9537,7 +9534,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -9560,7 +9557,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>27</v>
       </c>
@@ -9583,7 +9580,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>26</v>
       </c>
@@ -9606,7 +9603,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>29</v>
       </c>
@@ -9629,7 +9626,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>28</v>
       </c>
@@ -9652,7 +9649,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>30</v>
       </c>
@@ -9675,7 +9672,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>10</v>
       </c>
@@ -9698,7 +9695,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>11</v>
       </c>
@@ -9721,7 +9718,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>12</v>
       </c>
@@ -9744,7 +9741,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>13</v>
       </c>
@@ -9773,7 +9770,7 @@
         <v>0.1111111111111111</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>14</v>
       </c>
@@ -9796,7 +9793,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>15</v>
       </c>
@@ -9816,7 +9813,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>17</v>
       </c>
@@ -9836,7 +9833,7 @@
         <v>5400</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>16</v>
       </c>
@@ -9856,7 +9853,7 @@
         <v>22600</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>19</v>
       </c>
@@ -9876,7 +9873,7 @@
         <v>29400</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>18</v>
       </c>
@@ -9896,7 +9893,7 @@
         <v>-15300</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>32</v>
       </c>
@@ -9916,7 +9913,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>22</v>
       </c>
@@ -9936,7 +9933,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>23</v>
       </c>
@@ -9956,7 +9953,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>24</v>
       </c>
@@ -9976,7 +9973,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>25</v>
       </c>
@@ -10004,12 +10001,12 @@
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{63ADED8C-8B43-45F3-9000-B0A18B210D88}">
   <dimension ref="A1:F22"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -10017,7 +10014,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -10037,7 +10034,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -10057,7 +10054,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>176</v>
       </c>
@@ -10077,7 +10074,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>175</v>
       </c>
@@ -10097,7 +10094,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>177</v>
       </c>
@@ -10117,7 +10114,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>178</v>
       </c>
@@ -10137,7 +10134,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>10</v>
       </c>
@@ -10157,7 +10154,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>11</v>
       </c>
@@ -10177,7 +10174,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>12</v>
       </c>
@@ -10197,7 +10194,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>13</v>
       </c>
@@ -10217,7 +10214,7 @@
         <v>6.7000000000000004E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>14</v>
       </c>
@@ -10237,7 +10234,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>15</v>
       </c>
@@ -10254,7 +10251,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>174</v>
       </c>
@@ -10271,7 +10268,7 @@
         <v>27000</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>173</v>
       </c>
@@ -10288,7 +10285,7 @@
         <v>30000</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>179</v>
       </c>
@@ -10305,7 +10302,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>180</v>
       </c>
@@ -10330,12 +10327,12 @@
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{80A815BB-E5EC-4BD5-90B5-501DF3A65893}">
   <dimension ref="A1:G24"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -10343,7 +10340,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -10366,7 +10363,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -10389,7 +10386,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>185</v>
       </c>
@@ -10412,7 +10409,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>186</v>
       </c>
@@ -10435,7 +10432,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>187</v>
       </c>
@@ -10458,7 +10455,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>10</v>
       </c>
@@ -10481,7 +10478,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>11</v>
       </c>
@@ -10504,7 +10501,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>12</v>
       </c>
@@ -10527,7 +10524,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>13</v>
       </c>
@@ -10556,7 +10553,7 @@
         <v>0.16666666666666666</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>14</v>
       </c>
@@ -10579,7 +10576,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>15</v>
       </c>
@@ -10593,7 +10590,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>182</v>
       </c>
@@ -10607,7 +10604,7 @@
         <v>26600</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>183</v>
       </c>
@@ -10621,7 +10618,7 @@
         <v>11000</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>184</v>
       </c>
@@ -10635,10 +10632,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
       <c r="D22" s="6"/>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B24" s="6"/>
     </row>
   </sheetData>
@@ -10649,12 +10646,12 @@
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85A24F71-FDA1-43E6-8BBC-90604AA9909D}">
   <dimension ref="A1:I26"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -10662,7 +10659,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -10691,7 +10688,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -10720,7 +10717,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>185</v>
       </c>
@@ -10749,7 +10746,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>186</v>
       </c>
@@ -10778,7 +10775,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>187</v>
       </c>
@@ -10807,7 +10804,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>188</v>
       </c>
@@ -10836,7 +10833,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>189</v>
       </c>
@@ -10865,7 +10862,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>10</v>
       </c>
@@ -10894,7 +10891,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>11</v>
       </c>
@@ -10923,7 +10920,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>12</v>
       </c>
@@ -10952,7 +10949,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>13</v>
       </c>
@@ -10989,7 +10986,7 @@
         <v>0.16666666666666666</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>14</v>
       </c>
@@ -11018,7 +11015,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>15</v>
       </c>
@@ -11038,7 +11035,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>182</v>
       </c>
@@ -11058,7 +11055,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>183</v>
       </c>
@@ -11078,7 +11075,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>184</v>
       </c>
@@ -11098,7 +11095,7 @@
         <v>25000</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>190</v>
       </c>
@@ -11118,7 +11115,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>191</v>
       </c>
@@ -11138,7 +11135,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B26" s="6"/>
     </row>
   </sheetData>
@@ -11149,13 +11146,13 @@
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0082B2B7-692E-4F3C-8930-4804F9717528}">
   <dimension ref="A1:G24"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.453125" bestFit="1" customWidth="1"/>
     <col min="3" max="4" width="9" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -11163,18 +11160,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E3" t="s">
         <v>98</v>
@@ -11183,7 +11180,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -11203,29 +11200,29 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
+        <v>208</v>
+      </c>
+      <c r="B6">
+        <v>0</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
         <v>209</v>
-      </c>
-      <c r="B6">
-        <v>0</v>
-      </c>
-      <c r="C6">
-        <v>1</v>
-      </c>
-      <c r="D6">
-        <v>1</v>
-      </c>
-      <c r="E6">
-        <v>1</v>
-      </c>
-      <c r="F6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>210</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -11248,7 +11245,7 @@
       </c>
       <c r="G7" s="1"/>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>178</v>
       </c>
@@ -11268,7 +11265,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>10</v>
       </c>
@@ -11288,7 +11285,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>11</v>
       </c>
@@ -11308,7 +11305,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>12</v>
       </c>
@@ -11328,7 +11325,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>13</v>
       </c>
@@ -11353,7 +11350,7 @@
         <v>0.16666666666666666</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>14</v>
       </c>
@@ -11373,23 +11370,23 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>15</v>
       </c>
       <c r="B17" t="s">
+        <v>210</v>
+      </c>
+      <c r="C17" t="s">
         <v>211</v>
-      </c>
-      <c r="C17" t="s">
-        <v>212</v>
       </c>
       <c r="D17" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -11401,9 +11398,9 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B19" s="6">
         <v>2400</v>
@@ -11415,7 +11412,7 @@
         <v>-5000</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>180</v>
       </c>
@@ -11429,10 +11426,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
       <c r="D22" s="6"/>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B24" s="6"/>
     </row>
   </sheetData>
@@ -11443,12 +11440,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{872FBE85-5DBB-4A04-A80C-543C061B7441}">
   <dimension ref="A1:Q55"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -11456,12 +11453,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>1</v>
       </c>
-      <c r="B3" t="s">
-        <v>33</v>
+      <c r="B3" s="3" t="s">
+        <v>205</v>
       </c>
       <c r="C3" t="s">
         <v>33</v>
@@ -11469,7 +11466,7 @@
       <c r="D3" t="s">
         <v>33</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" t="s">
         <v>33</v>
       </c>
       <c r="F3" s="3" t="s">
@@ -11479,59 +11476,59 @@
         <v>33</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>33</v>
+        <v>219</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="J3" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="K3" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="K3" s="3" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>4</v>
       </c>
       <c r="B4" t="s">
+        <v>205</v>
+      </c>
+      <c r="C4" t="s">
         <v>50</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>48</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>49</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="F4" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F4" t="s">
+      <c r="G4" t="s">
         <v>5</v>
       </c>
-      <c r="G4" t="s">
+      <c r="H4" t="s">
+        <v>219</v>
+      </c>
+      <c r="I4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J4" t="s">
         <v>9</v>
       </c>
-      <c r="H4" t="s">
-        <v>6</v>
-      </c>
-      <c r="I4" t="s">
+      <c r="K4" t="s">
         <v>100</v>
       </c>
-      <c r="J4" t="s">
-        <v>206</v>
-      </c>
-      <c r="K4" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.35">
       <c r="O5" s="1"/>
       <c r="P5" s="1"/>
       <c r="Q5" s="1"/>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>52</v>
       </c>
@@ -11539,7 +11536,7 @@
         <v>1</v>
       </c>
       <c r="C6" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D6" s="1">
         <v>0</v>
@@ -11560,24 +11557,24 @@
         <v>0</v>
       </c>
       <c r="J6" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K6" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>53</v>
       </c>
       <c r="B7" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C7" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D7" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E7" s="1">
         <v>0</v>
@@ -11595,27 +11592,27 @@
         <v>0</v>
       </c>
       <c r="J7" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K7" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>54</v>
       </c>
       <c r="B8" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C8" s="1">
         <v>0</v>
       </c>
       <c r="D8" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E8" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F8" s="1">
         <v>0</v>
@@ -11630,18 +11627,18 @@
         <v>0</v>
       </c>
       <c r="J8" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K8" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>55</v>
       </c>
       <c r="B9" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C9" s="1">
         <v>0</v>
@@ -11650,10 +11647,10 @@
         <v>0</v>
       </c>
       <c r="E9" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F9" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G9" s="1">
         <v>0</v>
@@ -11665,18 +11662,18 @@
         <v>0</v>
       </c>
       <c r="J9" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K9" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>56</v>
       </c>
       <c r="B10" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C10" s="1">
         <v>0</v>
@@ -11688,10 +11685,10 @@
         <v>0</v>
       </c>
       <c r="F10" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G10" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H10" s="1">
         <v>0</v>
@@ -11700,18 +11697,18 @@
         <v>0</v>
       </c>
       <c r="J10" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K10" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>57</v>
       </c>
       <c r="B11" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C11" s="1">
         <v>0</v>
@@ -11726,10 +11723,10 @@
         <v>0</v>
       </c>
       <c r="G11" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H11" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I11" s="1">
         <v>0</v>
@@ -11738,15 +11735,15 @@
         <v>1</v>
       </c>
       <c r="K11" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>58</v>
       </c>
       <c r="B12" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C12" s="1">
         <v>0</v>
@@ -11767,19 +11764,19 @@
         <v>1</v>
       </c>
       <c r="I12" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J12" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K12" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O12" s="1"/>
       <c r="P12" s="1"/>
       <c r="Q12" s="1"/>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>59</v>
       </c>
@@ -11805,19 +11802,19 @@
         <v>0</v>
       </c>
       <c r="I13" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J13" s="1">
         <v>0</v>
       </c>
       <c r="K13" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O13" s="1"/>
       <c r="P13" s="1"/>
       <c r="Q13" s="1"/>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>10</v>
       </c>
@@ -11837,22 +11834,22 @@
         <v>1</v>
       </c>
       <c r="G15">
+        <v>1</v>
+      </c>
+      <c r="H15">
+        <v>-4</v>
+      </c>
+      <c r="I15">
         <v>5</v>
       </c>
-      <c r="H15">
+      <c r="J15">
         <v>5</v>
       </c>
-      <c r="I15">
+      <c r="K15">
         <v>2</v>
       </c>
-      <c r="J15">
-        <v>1</v>
-      </c>
-      <c r="K15">
-        <v>-4</v>
-      </c>
-    </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="17" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>11</v>
       </c>
@@ -11887,7 +11884,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>12</v>
       </c>
@@ -11922,16 +11919,16 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>13</v>
       </c>
       <c r="B19" s="4">
+        <f t="shared" ref="B19:L19" si="0">1/6</f>
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="C19" s="4">
         <f>1/6</f>
-        <v>0.16666666666666666</v>
-      </c>
-      <c r="C19" s="4">
-        <f t="shared" ref="C19:K19" si="0">1/6</f>
         <v>0.16666666666666666</v>
       </c>
       <c r="D19" s="4">
@@ -11969,7 +11966,7 @@
       <c r="O19" s="1"/>
       <c r="P19" s="1"/>
     </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>14</v>
       </c>
@@ -11983,22 +11980,22 @@
         <v>0</v>
       </c>
       <c r="E20">
+        <v>0</v>
+      </c>
+      <c r="F20">
         <v>2</v>
       </c>
-      <c r="F20">
-        <v>0</v>
-      </c>
       <c r="G20">
+        <v>0</v>
+      </c>
+      <c r="H20">
+        <v>0</v>
+      </c>
+      <c r="I20">
         <v>3</v>
       </c>
-      <c r="H20">
+      <c r="J20">
         <v>3</v>
-      </c>
-      <c r="I20">
-        <v>0</v>
-      </c>
-      <c r="J20">
-        <v>0</v>
       </c>
       <c r="K20">
         <v>0</v>
@@ -12006,11 +12003,11 @@
       <c r="O20" s="1"/>
       <c r="P20" s="1"/>
     </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:16" x14ac:dyDescent="0.35">
       <c r="J21" s="1"/>
       <c r="K21" s="1"/>
     </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>15</v>
       </c>
@@ -12039,7 +12036,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>42</v>
       </c>
@@ -12068,7 +12065,7 @@
         <v>17000</v>
       </c>
     </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>38</v>
       </c>
@@ -12097,7 +12094,7 @@
         <v>-1500</v>
       </c>
     </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>43</v>
       </c>
@@ -12126,7 +12123,7 @@
         <v>9500</v>
       </c>
     </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>37</v>
       </c>
@@ -12155,7 +12152,7 @@
         <v>7500</v>
       </c>
     </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>44</v>
       </c>
@@ -12184,7 +12181,7 @@
         <v>11000</v>
       </c>
     </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>36</v>
       </c>
@@ -12213,7 +12210,7 @@
         <v>11000</v>
       </c>
     </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>35</v>
       </c>
@@ -12242,7 +12239,7 @@
         <v>12000</v>
       </c>
     </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>45</v>
       </c>
@@ -12272,7 +12269,7 @@
       </c>
       <c r="M30" s="5"/>
     </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>20</v>
       </c>
@@ -12301,7 +12298,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>42</v>
       </c>
@@ -12330,7 +12327,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>38</v>
       </c>
@@ -12359,7 +12356,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>43</v>
       </c>
@@ -12388,7 +12385,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>37</v>
       </c>
@@ -12417,7 +12414,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>44</v>
       </c>
@@ -12446,7 +12443,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>36</v>
       </c>
@@ -12475,7 +12472,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>35</v>
       </c>
@@ -12504,7 +12501,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>45</v>
       </c>
@@ -12533,7 +12530,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>21</v>
       </c>
@@ -12562,7 +12559,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>42</v>
       </c>
@@ -12591,7 +12588,7 @@
         <v>-500</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>38</v>
       </c>
@@ -12620,7 +12617,7 @@
         <v>-300</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>43</v>
       </c>
@@ -12649,7 +12646,7 @@
         <v>-300</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>37</v>
       </c>
@@ -12678,7 +12675,7 @@
         <v>-500</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>44</v>
       </c>
@@ -12707,7 +12704,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>36</v>
       </c>
@@ -12736,7 +12733,7 @@
         <v>-500</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>35</v>
       </c>
@@ -12765,7 +12762,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>45</v>
       </c>
@@ -12794,7 +12791,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>22</v>
       </c>
@@ -12823,7 +12820,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>23</v>
       </c>
@@ -12852,7 +12849,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>24</v>
       </c>
@@ -12881,7 +12878,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>25</v>
       </c>
@@ -12920,12 +12917,12 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{72A1BB50-13AE-4CC0-80C4-28DCD15EA461}">
   <dimension ref="A1:F35"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -12933,7 +12930,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -12953,7 +12950,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -12973,7 +12970,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>62</v>
       </c>
@@ -12993,7 +12990,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>63</v>
       </c>
@@ -13013,7 +13010,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>64</v>
       </c>
@@ -13033,7 +13030,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>10</v>
       </c>
@@ -13053,7 +13050,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>11</v>
       </c>
@@ -13073,7 +13070,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>12</v>
       </c>
@@ -13093,7 +13090,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>13</v>
       </c>
@@ -13118,7 +13115,7 @@
         <v>0.16666666666666666</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>14</v>
       </c>
@@ -13138,7 +13135,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>15</v>
       </c>
@@ -13152,7 +13149,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>40</v>
       </c>
@@ -13166,7 +13163,7 @@
         <v>24100</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>34</v>
       </c>
@@ -13180,7 +13177,7 @@
         <v>48500</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>51</v>
       </c>
@@ -13194,7 +13191,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>20</v>
       </c>
@@ -13208,7 +13205,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>40</v>
       </c>
@@ -13222,7 +13219,7 @@
         <v>-9.57</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>34</v>
       </c>
@@ -13236,7 +13233,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>51</v>
       </c>
@@ -13250,7 +13247,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>21</v>
       </c>
@@ -13264,7 +13261,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>40</v>
       </c>
@@ -13278,7 +13275,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>34</v>
       </c>
@@ -13292,7 +13289,7 @@
         <v>-130</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>51</v>
       </c>
@@ -13306,7 +13303,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>22</v>
       </c>
@@ -13320,7 +13317,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>23</v>
       </c>
@@ -13334,7 +13331,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>24</v>
       </c>
@@ -13348,7 +13345,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>25</v>
       </c>
@@ -13370,12 +13367,12 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2FD421C-3FDE-4B9B-9D4C-89C90FA5CBD4}">
   <dimension ref="A1:D35"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -13383,7 +13380,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -13397,7 +13394,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -13411,7 +13408,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>65</v>
       </c>
@@ -13425,9 +13422,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -13439,7 +13436,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>64</v>
       </c>
@@ -13453,7 +13450,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>10</v>
       </c>
@@ -13467,7 +13464,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>11</v>
       </c>
@@ -13481,7 +13478,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>12</v>
       </c>
@@ -13495,7 +13492,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>13</v>
       </c>
@@ -13512,7 +13509,7 @@
         <v>0.125</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>14</v>
       </c>
@@ -13526,7 +13523,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>15</v>
       </c>
@@ -13540,7 +13537,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>60</v>
       </c>
@@ -13554,7 +13551,7 @@
         <v>25100</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>61</v>
       </c>
@@ -13568,7 +13565,7 @@
         <v>40000</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>51</v>
       </c>
@@ -13582,7 +13579,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>20</v>
       </c>
@@ -13596,7 +13593,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>60</v>
       </c>
@@ -13610,7 +13607,7 @@
         <v>-10.8</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>61</v>
       </c>
@@ -13624,7 +13621,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>51</v>
       </c>
@@ -13638,7 +13635,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>21</v>
       </c>
@@ -13652,7 +13649,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>60</v>
       </c>
@@ -13666,7 +13663,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>61</v>
       </c>
@@ -13680,7 +13677,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>51</v>
       </c>
@@ -13694,7 +13691,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>22</v>
       </c>
@@ -13708,7 +13705,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>23</v>
       </c>
@@ -13722,7 +13719,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>24</v>
       </c>
@@ -13736,7 +13733,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>25</v>
       </c>
@@ -13758,12 +13755,12 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34DCA22C-CAB3-4F04-A4C5-4849A205E620}">
   <dimension ref="A1:G32"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -13771,7 +13768,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -13788,7 +13785,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -13805,7 +13802,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>70</v>
       </c>
@@ -13822,7 +13819,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>71</v>
       </c>
@@ -13839,7 +13836,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>72</v>
       </c>
@@ -13856,7 +13853,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>10</v>
       </c>
@@ -13873,7 +13870,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>11</v>
       </c>
@@ -13890,7 +13887,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>12</v>
       </c>
@@ -13908,7 +13905,7 @@
       </c>
       <c r="F13" s="6"/>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>13</v>
       </c>
@@ -13930,7 +13927,7 @@
       </c>
       <c r="F14" s="6"/>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>14</v>
       </c>
@@ -13948,11 +13945,11 @@
       </c>
       <c r="F15" s="6"/>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
       <c r="F16" s="6"/>
       <c r="G16" s="6"/>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>15</v>
       </c>
@@ -13968,7 +13965,7 @@
       <c r="E17" s="6"/>
       <c r="G17" s="6"/>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>67</v>
       </c>
@@ -13984,7 +13981,7 @@
       <c r="E18" s="6"/>
       <c r="F18" s="6"/>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>68</v>
       </c>
@@ -13998,7 +13995,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>69</v>
       </c>
@@ -14012,20 +14009,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
       <c r="C29" s="6"/>
       <c r="D29" s="6"/>
       <c r="E29" s="6"/>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B30" s="6"/>
       <c r="E30" s="6"/>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B31" s="6"/>
       <c r="E31" s="6"/>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B32" s="6"/>
       <c r="C32" s="6"/>
       <c r="D32" s="6"/>
@@ -14038,12 +14035,12 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{63C858DD-A70E-43D6-BA3B-AC3F01588E20}">
   <dimension ref="A1:K47"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -14051,7 +14048,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -14086,7 +14083,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -14121,7 +14118,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>81</v>
       </c>
@@ -14156,7 +14153,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>87</v>
       </c>
@@ -14191,7 +14188,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>88</v>
       </c>
@@ -14226,7 +14223,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>84</v>
       </c>
@@ -14261,7 +14258,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>90</v>
       </c>
@@ -14296,7 +14293,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>85</v>
       </c>
@@ -14331,7 +14328,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>10</v>
       </c>
@@ -14366,7 +14363,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>11</v>
       </c>
@@ -14401,7 +14398,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>12</v>
       </c>
@@ -14436,7 +14433,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>13</v>
       </c>
@@ -14481,7 +14478,7 @@
         <v>0.16666666666666666</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>14</v>
       </c>
@@ -14516,7 +14513,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>15</v>
       </c>
@@ -14539,7 +14536,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>91</v>
       </c>
@@ -14562,7 +14559,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>92</v>
       </c>
@@ -14585,7 +14582,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>93</v>
       </c>
@@ -14608,7 +14605,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>94</v>
       </c>
@@ -14631,7 +14628,7 @@
         <v>30000</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>95</v>
       </c>
@@ -14654,7 +14651,7 @@
         <v>35000</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>80</v>
       </c>
@@ -14677,7 +14674,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>20</v>
       </c>
@@ -14700,7 +14697,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>91</v>
       </c>
@@ -14724,7 +14721,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>92</v>
       </c>
@@ -14747,7 +14744,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>93</v>
       </c>
@@ -14770,7 +14767,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>94</v>
       </c>
@@ -14794,7 +14791,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>95</v>
       </c>
@@ -14817,7 +14814,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>80</v>
       </c>
@@ -14840,7 +14837,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>21</v>
       </c>
@@ -14863,7 +14860,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>91</v>
       </c>
@@ -14886,7 +14883,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>92</v>
       </c>
@@ -14909,7 +14906,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>93</v>
       </c>
@@ -14932,7 +14929,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>94</v>
       </c>
@@ -14955,7 +14952,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>95</v>
       </c>
@@ -14978,7 +14975,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>80</v>
       </c>
@@ -15001,7 +14998,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>22</v>
       </c>
@@ -15024,7 +15021,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>23</v>
       </c>
@@ -15047,7 +15044,7 @@
         <v>0.63</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>24</v>
       </c>
@@ -15070,7 +15067,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>25</v>
       </c>
@@ -15101,12 +15098,12 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C555707-5676-48B4-9D6F-3E4989428F99}">
   <dimension ref="A1:K47"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -15114,7 +15111,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -15149,7 +15146,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -15184,7 +15181,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>86</v>
       </c>
@@ -15219,7 +15216,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>87</v>
       </c>
@@ -15254,7 +15251,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>88</v>
       </c>
@@ -15289,7 +15286,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>89</v>
       </c>
@@ -15324,7 +15321,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>90</v>
       </c>
@@ -15359,7 +15356,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>85</v>
       </c>
@@ -15394,7 +15391,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>10</v>
       </c>
@@ -15429,7 +15426,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>11</v>
       </c>
@@ -15464,7 +15461,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>12</v>
       </c>
@@ -15499,7 +15496,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>13</v>
       </c>
@@ -15544,7 +15541,7 @@
         <v>0.16666666666666666</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>14</v>
       </c>
@@ -15579,7 +15576,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>15</v>
       </c>
@@ -15602,7 +15599,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>91</v>
       </c>
@@ -15625,7 +15622,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>92</v>
       </c>
@@ -15648,7 +15645,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>93</v>
       </c>
@@ -15671,7 +15668,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>94</v>
       </c>
@@ -15688,13 +15685,13 @@
         <v>0</v>
       </c>
       <c r="F24" s="6">
-        <v>15000</v>
+        <v>18000</v>
       </c>
       <c r="G24" s="6">
         <v>30000</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>95</v>
       </c>
@@ -15708,7 +15705,7 @@
         <v>50000</v>
       </c>
       <c r="E25" s="6">
-        <v>15000</v>
+        <v>18000</v>
       </c>
       <c r="F25">
         <v>0</v>
@@ -15717,7 +15714,7 @@
         <v>35000</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>80</v>
       </c>
@@ -15740,7 +15737,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>20</v>
       </c>
@@ -15763,7 +15760,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>91</v>
       </c>
@@ -15787,7 +15784,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>92</v>
       </c>
@@ -15810,7 +15807,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>93</v>
       </c>
@@ -15833,7 +15830,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>94</v>
       </c>
@@ -15857,7 +15854,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>95</v>
       </c>
@@ -15880,7 +15877,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>80</v>
       </c>
@@ -15903,7 +15900,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>21</v>
       </c>
@@ -15926,7 +15923,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>91</v>
       </c>
@@ -15949,7 +15946,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>92</v>
       </c>
@@ -15972,7 +15969,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>93</v>
       </c>
@@ -15995,7 +15992,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>94</v>
       </c>
@@ -16018,7 +16015,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>95</v>
       </c>
@@ -16041,7 +16038,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>80</v>
       </c>
@@ -16064,7 +16061,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>22</v>
       </c>
@@ -16087,7 +16084,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>23</v>
       </c>
@@ -16110,7 +16107,7 @@
         <v>0.63</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>24</v>
       </c>
@@ -16133,7 +16130,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>25</v>
       </c>
@@ -16164,12 +16161,12 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9950AB7F-4462-43CF-828B-7DAAD62526DD}">
   <dimension ref="A1:K47"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -16177,7 +16174,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -16212,7 +16209,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -16247,7 +16244,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>81</v>
       </c>
@@ -16282,7 +16279,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>82</v>
       </c>
@@ -16317,7 +16314,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>83</v>
       </c>
@@ -16352,7 +16349,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>84</v>
       </c>
@@ -16387,7 +16384,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>90</v>
       </c>
@@ -16422,7 +16419,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>85</v>
       </c>
@@ -16457,7 +16454,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>10</v>
       </c>
@@ -16492,7 +16489,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>11</v>
       </c>
@@ -16527,7 +16524,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>12</v>
       </c>
@@ -16562,7 +16559,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>13</v>
       </c>
@@ -16607,7 +16604,7 @@
         <v>0.16666666666666666</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>14</v>
       </c>
@@ -16642,7 +16639,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>15</v>
       </c>
@@ -16665,7 +16662,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>76</v>
       </c>
@@ -16688,7 +16685,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>77</v>
       </c>
@@ -16711,7 +16708,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>78</v>
       </c>
@@ -16734,7 +16731,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>79</v>
       </c>
@@ -16757,7 +16754,7 @@
         <v>30000</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>96</v>
       </c>
@@ -16780,7 +16777,7 @@
         <v>35000</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>80</v>
       </c>
@@ -16803,7 +16800,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>20</v>
       </c>
@@ -16826,7 +16823,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>76</v>
       </c>
@@ -16850,7 +16847,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>77</v>
       </c>
@@ -16873,7 +16870,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>78</v>
       </c>
@@ -16896,7 +16893,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>79</v>
       </c>
@@ -16920,7 +16917,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>96</v>
       </c>
@@ -16943,7 +16940,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>80</v>
       </c>
@@ -16966,7 +16963,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>21</v>
       </c>
@@ -16989,7 +16986,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>76</v>
       </c>
@@ -17012,7 +17009,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>77</v>
       </c>
@@ -17035,7 +17032,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>78</v>
       </c>
@@ -17058,7 +17055,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>79</v>
       </c>
@@ -17081,7 +17078,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>96</v>
       </c>
@@ -17104,7 +17101,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>80</v>
       </c>
@@ -17127,7 +17124,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>22</v>
       </c>
@@ -17150,7 +17147,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>23</v>
       </c>
@@ -17173,7 +17170,7 @@
         <v>0.63</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>24</v>
       </c>
@@ -17196,7 +17193,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>25</v>
       </c>
